--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2454-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2454-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E104135B-2FE6-48EA-8D7C-057BF876A77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5805A4D-ECE4-43A5-9694-A790B7916293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{904FE01D-CD76-4EFD-BCA5-9D5F69AB82BF}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{7A0FB016-2FCF-4C34-83A9-52340E977BD2}"/>
   </bookViews>
   <sheets>
     <sheet name="2454-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1507,25 +1507,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD35824E-86FC-404B-85FD-431434BA8D73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2723BE4-63B9-464A-BF9A-F09A4C9B13E1}">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1583,7 +1583,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1679,7 +1679,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1759,7 +1759,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
         <v>2025</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="53">
         <v>2024</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="51">
         <v>2023</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>9.68</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="53">
         <v>2022</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>9.0500000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="51">
         <v>2021</v>
       </c>
@@ -2309,7 +2309,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="53">
         <v>2020</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="51">
         <v>2019</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="53">
         <v>2018</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="51">
         <v>2017</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="53">
         <v>2016</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2015</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="53">
         <v>2014</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="51">
         <v>2013</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="53">
         <v>2012</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>3.63</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="51">
         <v>2011</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>6.57</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="53">
         <v>2010</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="51">
         <v>2009</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="53">
         <v>2008</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>6.63</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="51">
         <v>2007</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="53">
         <v>2006</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="51">
         <v>2005</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="53">
         <v>2004</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="51">
         <v>2003</v>
       </c>
@@ -3281,7 +3281,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="53">
         <v>2002</v>
       </c>
@@ -3335,7 +3335,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="51">
         <v>2001</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="53">
         <v>2000</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="51" t="s">
         <v>38</v>
       </c>
